--- a/114/7/사각파이프.xlsx
+++ b/114/7/사각파이프.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\document\desktop\철강\사각파이프\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.251\Project1\html\114\7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18E08BE4-83A6-4E26-AAC8-F5C39249DF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A9ED3E-2F56-4CB0-AC67-42303FBD687D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60240" yWindow="1830" windowWidth="21600" windowHeight="11235" xr2:uid="{9B109079-7BBD-4416-9B34-D673AA13B087}"/>
+    <workbookView xWindow="-21710" yWindow="-8720" windowWidth="21820" windowHeight="37900" xr2:uid="{9B109079-7BBD-4416-9B34-D673AA13B087}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="98">
   <si>
     <t>품명</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -394,9 +394,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,19 +478,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -830,203 +830,203 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B3FBFC1-EFE9-4666-A349-15B3CFD78B93}">
   <dimension ref="B2:F110"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="12.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="258" max="258" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="259" max="259" width="18" bestFit="1" customWidth="1"/>
-    <col min="260" max="260" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="514" max="514" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="260" max="260" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="515" max="515" width="18" bestFit="1" customWidth="1"/>
-    <col min="516" max="516" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="770" max="770" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="516" max="516" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="770" max="770" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="771" max="771" width="18" bestFit="1" customWidth="1"/>
-    <col min="772" max="772" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="1026" max="1026" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="772" max="772" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="1026" max="1026" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="1027" max="1027" width="18" bestFit="1" customWidth="1"/>
-    <col min="1028" max="1028" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="1282" max="1282" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="1028" max="1028" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="1282" max="1282" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="1283" max="1283" width="18" bestFit="1" customWidth="1"/>
-    <col min="1284" max="1284" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="1538" max="1538" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="1284" max="1284" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="1538" max="1538" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="1539" max="1539" width="18" bestFit="1" customWidth="1"/>
-    <col min="1540" max="1540" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="1794" max="1794" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="1540" max="1540" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="1794" max="1794" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="1795" max="1795" width="18" bestFit="1" customWidth="1"/>
-    <col min="1796" max="1796" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2050" max="2050" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="1796" max="1796" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2050" max="2050" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2051" max="2051" width="18" bestFit="1" customWidth="1"/>
-    <col min="2052" max="2052" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2306" max="2306" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="2052" max="2052" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2306" max="2306" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2307" max="2307" width="18" bestFit="1" customWidth="1"/>
-    <col min="2308" max="2308" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2562" max="2562" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="2308" max="2308" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2562" max="2562" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2563" max="2563" width="18" bestFit="1" customWidth="1"/>
-    <col min="2564" max="2564" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="2818" max="2818" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="2564" max="2564" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="2818" max="2818" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2819" max="2819" width="18" bestFit="1" customWidth="1"/>
-    <col min="2820" max="2820" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3074" max="3074" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="2820" max="2820" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3074" max="3074" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="3075" max="3075" width="18" bestFit="1" customWidth="1"/>
-    <col min="3076" max="3076" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3330" max="3330" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="3076" max="3076" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3330" max="3330" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="3331" max="3331" width="18" bestFit="1" customWidth="1"/>
-    <col min="3332" max="3332" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3586" max="3586" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="3332" max="3332" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3586" max="3586" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="3587" max="3587" width="18" bestFit="1" customWidth="1"/>
-    <col min="3588" max="3588" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3842" max="3842" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="3588" max="3588" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="3842" max="3842" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="3843" max="3843" width="18" bestFit="1" customWidth="1"/>
-    <col min="3844" max="3844" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4098" max="4098" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="3844" max="3844" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="4098" max="4098" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4099" max="4099" width="18" bestFit="1" customWidth="1"/>
-    <col min="4100" max="4100" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4354" max="4354" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="4100" max="4100" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="4354" max="4354" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4355" max="4355" width="18" bestFit="1" customWidth="1"/>
-    <col min="4356" max="4356" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4610" max="4610" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="4356" max="4356" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="4610" max="4610" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4611" max="4611" width="18" bestFit="1" customWidth="1"/>
-    <col min="4612" max="4612" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4866" max="4866" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="4612" max="4612" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="4866" max="4866" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4867" max="4867" width="18" bestFit="1" customWidth="1"/>
-    <col min="4868" max="4868" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5122" max="5122" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="4868" max="4868" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5122" max="5122" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5123" max="5123" width="18" bestFit="1" customWidth="1"/>
-    <col min="5124" max="5124" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5378" max="5378" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="5124" max="5124" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5378" max="5378" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5379" max="5379" width="18" bestFit="1" customWidth="1"/>
-    <col min="5380" max="5380" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5634" max="5634" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="5380" max="5380" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5634" max="5634" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5635" max="5635" width="18" bestFit="1" customWidth="1"/>
-    <col min="5636" max="5636" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="5890" max="5890" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="5636" max="5636" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="5890" max="5890" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5891" max="5891" width="18" bestFit="1" customWidth="1"/>
-    <col min="5892" max="5892" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="6146" max="6146" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="5892" max="5892" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6146" max="6146" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6147" max="6147" width="18" bestFit="1" customWidth="1"/>
-    <col min="6148" max="6148" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="6402" max="6402" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="6148" max="6148" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6402" max="6402" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6403" max="6403" width="18" bestFit="1" customWidth="1"/>
-    <col min="6404" max="6404" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="6658" max="6658" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="6404" max="6404" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6658" max="6658" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6659" max="6659" width="18" bestFit="1" customWidth="1"/>
-    <col min="6660" max="6660" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="6914" max="6914" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="6660" max="6660" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6914" max="6914" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6915" max="6915" width="18" bestFit="1" customWidth="1"/>
-    <col min="6916" max="6916" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7170" max="7170" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="6916" max="6916" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7170" max="7170" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="7171" max="7171" width="18" bestFit="1" customWidth="1"/>
-    <col min="7172" max="7172" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7426" max="7426" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="7172" max="7172" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7426" max="7426" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="7427" max="7427" width="18" bestFit="1" customWidth="1"/>
-    <col min="7428" max="7428" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7682" max="7682" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="7428" max="7428" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7682" max="7682" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="7683" max="7683" width="18" bestFit="1" customWidth="1"/>
-    <col min="7684" max="7684" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="7938" max="7938" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="7684" max="7684" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="7938" max="7938" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="7939" max="7939" width="18" bestFit="1" customWidth="1"/>
-    <col min="7940" max="7940" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="8194" max="8194" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="7940" max="7940" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="8194" max="8194" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8195" max="8195" width="18" bestFit="1" customWidth="1"/>
-    <col min="8196" max="8196" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="8450" max="8450" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="8196" max="8196" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="8450" max="8450" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8451" max="8451" width="18" bestFit="1" customWidth="1"/>
-    <col min="8452" max="8452" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="8706" max="8706" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="8452" max="8452" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="8706" max="8706" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8707" max="8707" width="18" bestFit="1" customWidth="1"/>
-    <col min="8708" max="8708" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="8962" max="8962" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="8708" max="8708" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="8962" max="8962" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8963" max="8963" width="18" bestFit="1" customWidth="1"/>
-    <col min="8964" max="8964" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="9218" max="9218" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="8964" max="8964" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="9218" max="9218" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="9219" max="9219" width="18" bestFit="1" customWidth="1"/>
-    <col min="9220" max="9220" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="9474" max="9474" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="9220" max="9220" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="9474" max="9474" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="9475" max="9475" width="18" bestFit="1" customWidth="1"/>
-    <col min="9476" max="9476" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="9730" max="9730" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="9476" max="9476" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="9730" max="9730" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="9731" max="9731" width="18" bestFit="1" customWidth="1"/>
-    <col min="9732" max="9732" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="9986" max="9986" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="9732" max="9732" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="9986" max="9986" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="9987" max="9987" width="18" bestFit="1" customWidth="1"/>
-    <col min="9988" max="9988" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="10242" max="10242" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="9988" max="9988" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="10242" max="10242" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10243" max="10243" width="18" bestFit="1" customWidth="1"/>
-    <col min="10244" max="10244" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="10498" max="10498" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="10244" max="10244" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="10498" max="10498" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10499" max="10499" width="18" bestFit="1" customWidth="1"/>
-    <col min="10500" max="10500" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="10754" max="10754" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="10500" max="10500" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="10754" max="10754" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10755" max="10755" width="18" bestFit="1" customWidth="1"/>
-    <col min="10756" max="10756" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="11010" max="11010" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="10756" max="10756" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11010" max="11010" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="11011" max="11011" width="18" bestFit="1" customWidth="1"/>
-    <col min="11012" max="11012" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="11266" max="11266" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="11012" max="11012" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11266" max="11266" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="11267" max="11267" width="18" bestFit="1" customWidth="1"/>
-    <col min="11268" max="11268" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="11522" max="11522" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="11268" max="11268" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11522" max="11522" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="11523" max="11523" width="18" bestFit="1" customWidth="1"/>
-    <col min="11524" max="11524" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="11778" max="11778" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="11524" max="11524" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="11778" max="11778" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="11779" max="11779" width="18" bestFit="1" customWidth="1"/>
-    <col min="11780" max="11780" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12034" max="12034" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="11780" max="11780" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12034" max="12034" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12035" max="12035" width="18" bestFit="1" customWidth="1"/>
-    <col min="12036" max="12036" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12290" max="12290" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="12036" max="12036" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12290" max="12290" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12291" max="12291" width="18" bestFit="1" customWidth="1"/>
-    <col min="12292" max="12292" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12546" max="12546" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="12292" max="12292" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12546" max="12546" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12547" max="12547" width="18" bestFit="1" customWidth="1"/>
-    <col min="12548" max="12548" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="12802" max="12802" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="12548" max="12548" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="12802" max="12802" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12803" max="12803" width="18" bestFit="1" customWidth="1"/>
-    <col min="12804" max="12804" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="13058" max="13058" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="12804" max="12804" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="13058" max="13058" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="13059" max="13059" width="18" bestFit="1" customWidth="1"/>
-    <col min="13060" max="13060" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="13314" max="13314" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="13060" max="13060" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="13314" max="13314" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="13315" max="13315" width="18" bestFit="1" customWidth="1"/>
-    <col min="13316" max="13316" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="13570" max="13570" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="13316" max="13316" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="13570" max="13570" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="13571" max="13571" width="18" bestFit="1" customWidth="1"/>
-    <col min="13572" max="13572" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="13826" max="13826" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="13572" max="13572" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="13826" max="13826" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="13827" max="13827" width="18" bestFit="1" customWidth="1"/>
-    <col min="13828" max="13828" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14082" max="14082" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="13828" max="13828" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="14082" max="14082" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="14083" max="14083" width="18" bestFit="1" customWidth="1"/>
-    <col min="14084" max="14084" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14338" max="14338" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="14084" max="14084" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="14338" max="14338" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="14339" max="14339" width="18" bestFit="1" customWidth="1"/>
-    <col min="14340" max="14340" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14594" max="14594" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="14340" max="14340" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="14594" max="14594" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="14595" max="14595" width="18" bestFit="1" customWidth="1"/>
-    <col min="14596" max="14596" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="14850" max="14850" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="14596" max="14596" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="14850" max="14850" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="14851" max="14851" width="18" bestFit="1" customWidth="1"/>
-    <col min="14852" max="14852" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="15106" max="15106" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="14852" max="14852" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="15106" max="15106" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="15107" max="15107" width="18" bestFit="1" customWidth="1"/>
-    <col min="15108" max="15108" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="15362" max="15362" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="15108" max="15108" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="15362" max="15362" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="15363" max="15363" width="18" bestFit="1" customWidth="1"/>
-    <col min="15364" max="15364" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="15618" max="15618" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="15364" max="15364" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="15618" max="15618" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="15619" max="15619" width="18" bestFit="1" customWidth="1"/>
-    <col min="15620" max="15620" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="15874" max="15874" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="15620" max="15620" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="15874" max="15874" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="15875" max="15875" width="18" bestFit="1" customWidth="1"/>
-    <col min="15876" max="15876" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="16130" max="16130" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="15876" max="15876" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="16130" max="16130" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="16131" max="16131" width="18" bestFit="1" customWidth="1"/>
-    <col min="16132" max="16132" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="16132" max="16132" width="12.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6">
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6">
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>0.64200000000000002</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6">
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>0.69699999999999995</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6">
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>0.872</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6">
       <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>0.86699999999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6">
       <c r="B12" s="1" t="s">
         <v>4</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6">
       <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6">
       <c r="B14" s="1" t="s">
         <v>4</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6">
       <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6">
       <c r="B16" s="1" t="s">
         <v>4</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:4">
       <c r="B17" s="1" t="s">
         <v>4</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:4">
       <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:4">
       <c r="B19" s="1" t="s">
         <v>4</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:4">
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:4">
       <c r="B21" s="1" t="s">
         <v>4</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:4">
       <c r="B22" s="1" t="s">
         <v>4</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:4">
       <c r="B23" s="1" t="s">
         <v>4</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:4">
       <c r="B24" s="1" t="s">
         <v>4</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:4">
       <c r="B25" s="1" t="s">
         <v>4</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:4">
       <c r="B26" s="1" t="s">
         <v>4</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:4">
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:4">
       <c r="B28" s="1" t="s">
         <v>4</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:4">
       <c r="B29" s="1" t="s">
         <v>4</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:4">
       <c r="B30" s="1" t="s">
         <v>4</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:4">
       <c r="B31" s="1" t="s">
         <v>4</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:4">
       <c r="B32" s="1" t="s">
         <v>4</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:4">
       <c r="B33" s="1" t="s">
         <v>4</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:4">
       <c r="B34" s="1" t="s">
         <v>4</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:4">
       <c r="B35" s="1" t="s">
         <v>4</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:4">
       <c r="B36" s="1" t="s">
         <v>4</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:4">
       <c r="B37" s="1" t="s">
         <v>4</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>38.21</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:4">
       <c r="B38" s="1" t="s">
         <v>4</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:4">
       <c r="B39" s="1" t="s">
         <v>4</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:4">
       <c r="B40" s="1" t="s">
         <v>4</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:4">
       <c r="B41" s="1" t="s">
         <v>4</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:4">
       <c r="B42" s="1" t="s">
         <v>4</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:4">
       <c r="B43" s="1" t="s">
         <v>4</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:4">
       <c r="B44" s="1" t="s">
         <v>4</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:4">
       <c r="B45" s="1" t="s">
         <v>4</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:4">
       <c r="B46" s="1" t="s">
         <v>4</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>0.86799999999999999</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:4">
       <c r="B47" s="1" t="s">
         <v>4</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>1.1240000000000001</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:4">
       <c r="B48" s="1" t="s">
         <v>4</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>1.0529999999999999</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:4">
       <c r="B49" s="1" t="s">
         <v>4</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>1.375</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:4">
       <c r="B50" s="1" t="s">
         <v>4</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:4">
       <c r="B51" s="1" t="s">
         <v>4</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:4">
       <c r="B52" s="1" t="s">
         <v>4</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:4">
       <c r="B53" s="1" t="s">
         <v>4</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:4">
       <c r="B54" s="1" t="s">
         <v>4</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:4">
       <c r="B55" s="1" t="s">
         <v>4</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:4">
       <c r="B56" s="1" t="s">
         <v>4</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:4">
       <c r="B57" s="1" t="s">
         <v>4</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:4">
       <c r="B58" s="1" t="s">
         <v>4</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:4">
       <c r="B59" s="1" t="s">
         <v>4</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:4">
       <c r="B60" s="1" t="s">
         <v>4</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:4">
       <c r="B61" s="1" t="s">
         <v>4</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:4">
       <c r="B62" s="1" t="s">
         <v>4</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:4">
       <c r="B63" s="1" t="s">
         <v>4</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:4">
       <c r="B64" s="1" t="s">
         <v>4</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:4">
       <c r="B65" s="1" t="s">
         <v>4</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:4">
       <c r="B66" s="1" t="s">
         <v>4</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:4">
       <c r="B67" s="1" t="s">
         <v>4</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:4">
       <c r="B68" s="1" t="s">
         <v>4</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:4">
       <c r="B69" s="1" t="s">
         <v>4</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:4">
       <c r="B70" s="1" t="s">
         <v>4</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:4">
       <c r="B71" s="1" t="s">
         <v>4</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:4">
       <c r="B72" s="1" t="s">
         <v>4</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:4">
       <c r="B73" s="1" t="s">
         <v>4</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:4">
       <c r="B74" s="1" t="s">
         <v>4</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:4">
       <c r="B75" s="1" t="s">
         <v>4</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:4">
       <c r="B76" s="1" t="s">
         <v>4</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:4">
       <c r="B77" s="1" t="s">
         <v>4</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:4">
       <c r="B78" s="1" t="s">
         <v>4</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:4">
       <c r="B79" s="1" t="s">
         <v>4</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:4">
       <c r="B80" s="1" t="s">
         <v>4</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:4">
       <c r="B81" s="1" t="s">
         <v>4</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:4">
       <c r="B82" s="1" t="s">
         <v>4</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:4">
       <c r="B83" s="1" t="s">
         <v>4</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:4">
       <c r="B84" s="1" t="s">
         <v>4</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>67.900000000000006</v>
       </c>
     </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:4">
       <c r="B85" s="1" t="s">
         <v>4</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:4">
       <c r="B86" s="1" t="s">
         <v>4</v>
       </c>
@@ -1976,8 +1976,10 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B87" s="1"/>
+    <row r="87" spans="2:4">
+      <c r="B87" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C87" s="3" t="s">
         <v>91</v>
       </c>
@@ -1985,8 +1987,10 @@
         <v>86.8</v>
       </c>
     </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B88" s="1"/>
+    <row r="88" spans="2:4">
+      <c r="B88" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C88" s="3" t="s">
         <v>89</v>
       </c>
@@ -1994,8 +1998,10 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B89" s="1"/>
+    <row r="89" spans="2:4">
+      <c r="B89" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C89" s="3" t="s">
         <v>90</v>
       </c>
@@ -2003,8 +2009,10 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B90" s="1"/>
+    <row r="90" spans="2:4">
+      <c r="B90" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C90" s="3" t="s">
         <v>91</v>
       </c>
@@ -2012,8 +2020,10 @@
         <v>86.8</v>
       </c>
     </row>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B91" s="1"/>
+    <row r="91" spans="2:4">
+      <c r="B91" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C91" s="3" t="s">
         <v>92</v>
       </c>
@@ -2021,8 +2031,10 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B92" s="1"/>
+    <row r="92" spans="2:4">
+      <c r="B92" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C92" s="3" t="s">
         <v>93</v>
       </c>
@@ -2030,8 +2042,10 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B93" s="1"/>
+    <row r="93" spans="2:4">
+      <c r="B93" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C93" s="3" t="s">
         <v>94</v>
       </c>
@@ -2039,8 +2053,10 @@
         <v>86.8</v>
       </c>
     </row>
-    <row r="94" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B94" s="1"/>
+    <row r="94" spans="2:4">
+      <c r="B94" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C94" s="3" t="s">
         <v>95</v>
       </c>
@@ -2048,8 +2064,10 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="95" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B95" s="1"/>
+    <row r="95" spans="2:4">
+      <c r="B95" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C95" s="3" t="s">
         <v>96</v>
       </c>
@@ -2057,8 +2075,10 @@
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="96" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B96" s="1"/>
+    <row r="96" spans="2:4">
+      <c r="B96" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="C96" s="3" t="s">
         <v>97</v>
       </c>
@@ -2066,67 +2086,67 @@
         <v>106</v>
       </c>
     </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:4">
       <c r="B97" s="1"/>
       <c r="C97" s="5"/>
       <c r="D97" s="6"/>
     </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:4">
       <c r="B98" s="1"/>
       <c r="C98" s="7"/>
       <c r="D98" s="8"/>
     </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:4">
       <c r="B99" s="1"/>
       <c r="C99" s="7"/>
       <c r="D99" s="8"/>
     </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:4">
       <c r="B100" s="1"/>
       <c r="C100" s="7"/>
       <c r="D100" s="8"/>
     </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:4">
       <c r="B101" s="1"/>
       <c r="C101" s="7"/>
       <c r="D101" s="8"/>
     </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:4">
       <c r="B102" s="1"/>
       <c r="C102" s="7"/>
       <c r="D102" s="8"/>
     </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:4">
       <c r="B103" s="1"/>
       <c r="C103" s="7"/>
       <c r="D103" s="8"/>
     </row>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="104" spans="2:4">
       <c r="B104" s="1"/>
       <c r="C104" s="7"/>
       <c r="D104" s="8"/>
     </row>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="105" spans="2:4">
       <c r="C105" s="7"/>
       <c r="D105" s="8"/>
     </row>
-    <row r="106" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="106" spans="2:4">
       <c r="C106" s="7"/>
       <c r="D106" s="8"/>
     </row>
-    <row r="107" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:4">
       <c r="C107" s="7"/>
       <c r="D107" s="8"/>
     </row>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="108" spans="2:4">
       <c r="C108" s="7"/>
       <c r="D108" s="8"/>
     </row>
-    <row r="109" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="109" spans="2:4">
       <c r="C109" s="7"/>
       <c r="D109" s="8"/>
     </row>
-    <row r="110" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="110" spans="2:4">
       <c r="C110" s="7"/>
       <c r="D110" s="8"/>
     </row>
